--- a/demo-excel/09-Talent-Review-9-Box-Kompetensi-demo.xlsx
+++ b/demo-excel/09-Talent-Review-9-Box-Kompetensi-demo.xlsx
@@ -11,9 +11,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PARAMETER" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KARYAWAN" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RINGKASAN" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FULL-MATRIKS_9BOX" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FULL-KOMPETENSI" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FULL-SUKSESI" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FULL-DASHBOARD" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'KARYAWAN'!$A$5:$W$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'KARYAWAN'!$A$5:$W$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -27,7 +31,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.0%;(0.0%);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -109,6 +113,29 @@
       <i val="1"/>
       <color rgb="005B6B82"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C0392B"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000B1A30"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="0033445C"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001E8449"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="7">
@@ -214,7 +241,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -315,6 +342,12 @@
     <xf numFmtId="167" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -963,7 +996,7 @@
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Data karyawan (kapasitas 40): kinerja, potensi, 6 kompetensi; skor, gap, kotak 9-box, dan tindakan terisi otomatis.</t>
+          <t>Data karyawan (kapasitas 20): kinerja, potensi, 6 kompetensi; skor, gap, kotak 9-box, dan tindakan terisi otomatis.</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X45"/>
+  <dimension ref="A1:X25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1575,7 +1608,7 @@
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Kapasitas 40 baris. Skor 1-5 dengan satu desimal.</t>
+          <t>Kapasitas 20 baris. Skor 1-5 dengan satu desimal.</t>
         </is>
       </c>
     </row>
@@ -2784,58 +2817,20 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="27" t="inlineStr">
-        <is>
-          <t>K-013</t>
-        </is>
-      </c>
-      <c r="B18" s="27" t="inlineStr">
-        <is>
-          <t>Lina Wijaya</t>
-        </is>
-      </c>
-      <c r="C18" s="27" t="inlineStr">
-        <is>
-          <t>Operasional</t>
-        </is>
-      </c>
-      <c r="D18" s="27" t="inlineStr">
-        <is>
-          <t>Spesialis</t>
-        </is>
-      </c>
-      <c r="E18" s="31" t="inlineStr">
-        <is>
-          <t>G5</t>
-        </is>
-      </c>
-      <c r="F18" s="32" t="n">
-        <v>43258</v>
-      </c>
-      <c r="G18" s="33" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H18" s="33" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="I18" s="33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J18" s="33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K18" s="33" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L18" s="33" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="M18" s="33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N18" s="33" t="n">
-        <v>1.9</v>
-      </c>
+      <c r="A18" s="27" t="n"/>
+      <c r="B18" s="27" t="n"/>
+      <c r="C18" s="27" t="n"/>
+      <c r="D18" s="27" t="n"/>
+      <c r="E18" s="31" t="n"/>
+      <c r="F18" s="32" t="n"/>
+      <c r="G18" s="33" t="n"/>
+      <c r="H18" s="33" t="n"/>
+      <c r="I18" s="33" t="n"/>
+      <c r="J18" s="33" t="n"/>
+      <c r="K18" s="33" t="n"/>
+      <c r="L18" s="33" t="n"/>
+      <c r="M18" s="33" t="n"/>
+      <c r="N18" s="33" t="n"/>
       <c r="O18" s="34">
         <f>IF($A18="","",ROUND((PARAMETER!$C$5-F18)/365.25,1))</f>
         <v/>
@@ -2874,58 +2869,20 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="27" t="inlineStr">
-        <is>
-          <t>K-014</t>
-        </is>
-      </c>
-      <c r="B19" s="27" t="inlineStr">
-        <is>
-          <t>Ulfa Permana</t>
-        </is>
-      </c>
-      <c r="C19" s="27" t="inlineStr">
-        <is>
-          <t>Keuangan</t>
-        </is>
-      </c>
-      <c r="D19" s="27" t="inlineStr">
-        <is>
-          <t>Staf</t>
-        </is>
-      </c>
-      <c r="E19" s="31" t="inlineStr">
-        <is>
-          <t>G5</t>
-        </is>
-      </c>
-      <c r="F19" s="32" t="n">
-        <v>44779</v>
-      </c>
-      <c r="G19" s="33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H19" s="33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I19" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="J19" s="33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K19" s="33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L19" s="33" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="M19" s="33" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N19" s="33" t="n">
-        <v>2.7</v>
-      </c>
+      <c r="A19" s="27" t="n"/>
+      <c r="B19" s="27" t="n"/>
+      <c r="C19" s="27" t="n"/>
+      <c r="D19" s="27" t="n"/>
+      <c r="E19" s="31" t="n"/>
+      <c r="F19" s="32" t="n"/>
+      <c r="G19" s="33" t="n"/>
+      <c r="H19" s="33" t="n"/>
+      <c r="I19" s="33" t="n"/>
+      <c r="J19" s="33" t="n"/>
+      <c r="K19" s="33" t="n"/>
+      <c r="L19" s="33" t="n"/>
+      <c r="M19" s="33" t="n"/>
+      <c r="N19" s="33" t="n"/>
       <c r="O19" s="34">
         <f>IF($A19="","",ROUND((PARAMETER!$C$5-F19)/365.25,1))</f>
         <v/>
@@ -2964,58 +2921,20 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="inlineStr">
-        <is>
-          <t>K-015</t>
-        </is>
-      </c>
-      <c r="B20" s="27" t="inlineStr">
-        <is>
-          <t>Putra Saputra</t>
-        </is>
-      </c>
-      <c r="C20" s="27" t="inlineStr">
-        <is>
-          <t>Operasional</t>
-        </is>
-      </c>
-      <c r="D20" s="27" t="inlineStr">
-        <is>
-          <t>Manajer</t>
-        </is>
-      </c>
-      <c r="E20" s="31" t="inlineStr">
-        <is>
-          <t>G4</t>
-        </is>
-      </c>
-      <c r="F20" s="32" t="n">
-        <v>44457</v>
-      </c>
-      <c r="G20" s="33" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H20" s="33" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I20" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="J20" s="33" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K20" s="33" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L20" s="33" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="M20" s="33" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N20" s="33" t="n">
-        <v>4.4</v>
-      </c>
+      <c r="A20" s="27" t="n"/>
+      <c r="B20" s="27" t="n"/>
+      <c r="C20" s="27" t="n"/>
+      <c r="D20" s="27" t="n"/>
+      <c r="E20" s="31" t="n"/>
+      <c r="F20" s="32" t="n"/>
+      <c r="G20" s="33" t="n"/>
+      <c r="H20" s="33" t="n"/>
+      <c r="I20" s="33" t="n"/>
+      <c r="J20" s="33" t="n"/>
+      <c r="K20" s="33" t="n"/>
+      <c r="L20" s="33" t="n"/>
+      <c r="M20" s="33" t="n"/>
+      <c r="N20" s="33" t="n"/>
       <c r="O20" s="34">
         <f>IF($A20="","",ROUND((PARAMETER!$C$5-F20)/365.25,1))</f>
         <v/>
@@ -3054,58 +2973,20 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="27" t="inlineStr">
-        <is>
-          <t>K-016</t>
-        </is>
-      </c>
-      <c r="B21" s="27" t="inlineStr">
-        <is>
-          <t>Tegar Permana</t>
-        </is>
-      </c>
-      <c r="C21" s="27" t="inlineStr">
-        <is>
-          <t>Operasional</t>
-        </is>
-      </c>
-      <c r="D21" s="27" t="inlineStr">
-        <is>
-          <t>Spesialis</t>
-        </is>
-      </c>
-      <c r="E21" s="31" t="inlineStr">
-        <is>
-          <t>G3</t>
-        </is>
-      </c>
-      <c r="F21" s="32" t="n">
-        <v>44297</v>
-      </c>
-      <c r="G21" s="33" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H21" s="33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I21" s="33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J21" s="33" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K21" s="33" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L21" s="33" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="M21" s="33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N21" s="33" t="n">
-        <v>3.2</v>
-      </c>
+      <c r="A21" s="27" t="n"/>
+      <c r="B21" s="27" t="n"/>
+      <c r="C21" s="27" t="n"/>
+      <c r="D21" s="27" t="n"/>
+      <c r="E21" s="31" t="n"/>
+      <c r="F21" s="32" t="n"/>
+      <c r="G21" s="33" t="n"/>
+      <c r="H21" s="33" t="n"/>
+      <c r="I21" s="33" t="n"/>
+      <c r="J21" s="33" t="n"/>
+      <c r="K21" s="33" t="n"/>
+      <c r="L21" s="33" t="n"/>
+      <c r="M21" s="33" t="n"/>
+      <c r="N21" s="33" t="n"/>
       <c r="O21" s="34">
         <f>IF($A21="","",ROUND((PARAMETER!$C$5-F21)/365.25,1))</f>
         <v/>
@@ -3144,58 +3025,20 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="27" t="inlineStr">
-        <is>
-          <t>K-017</t>
-        </is>
-      </c>
-      <c r="B22" s="27" t="inlineStr">
-        <is>
-          <t>Jihan Wijaya</t>
-        </is>
-      </c>
-      <c r="C22" s="27" t="inlineStr">
-        <is>
-          <t>Operasional</t>
-        </is>
-      </c>
-      <c r="D22" s="27" t="inlineStr">
-        <is>
-          <t>Senior Staf</t>
-        </is>
-      </c>
-      <c r="E22" s="31" t="inlineStr">
-        <is>
-          <t>G4</t>
-        </is>
-      </c>
-      <c r="F22" s="32" t="n">
-        <v>44392</v>
-      </c>
-      <c r="G22" s="33" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H22" s="33" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I22" s="33" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J22" s="33" t="n">
-        <v>5</v>
-      </c>
-      <c r="K22" s="33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L22" s="33" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="M22" s="33" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N22" s="33" t="n">
-        <v>4.8</v>
-      </c>
+      <c r="A22" s="27" t="n"/>
+      <c r="B22" s="27" t="n"/>
+      <c r="C22" s="27" t="n"/>
+      <c r="D22" s="27" t="n"/>
+      <c r="E22" s="31" t="n"/>
+      <c r="F22" s="32" t="n"/>
+      <c r="G22" s="33" t="n"/>
+      <c r="H22" s="33" t="n"/>
+      <c r="I22" s="33" t="n"/>
+      <c r="J22" s="33" t="n"/>
+      <c r="K22" s="33" t="n"/>
+      <c r="L22" s="33" t="n"/>
+      <c r="M22" s="33" t="n"/>
+      <c r="N22" s="33" t="n"/>
       <c r="O22" s="34">
         <f>IF($A22="","",ROUND((PARAMETER!$C$5-F22)/365.25,1))</f>
         <v/>
@@ -3234,58 +3077,20 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="27" t="inlineStr">
-        <is>
-          <t>K-018</t>
-        </is>
-      </c>
-      <c r="B23" s="27" t="inlineStr">
-        <is>
-          <t>Yusuf Maulana</t>
-        </is>
-      </c>
-      <c r="C23" s="27" t="inlineStr">
-        <is>
-          <t>Pemasaran</t>
-        </is>
-      </c>
-      <c r="D23" s="27" t="inlineStr">
-        <is>
-          <t>Staf</t>
-        </is>
-      </c>
-      <c r="E23" s="31" t="inlineStr">
-        <is>
-          <t>G4</t>
-        </is>
-      </c>
-      <c r="F23" s="32" t="n">
-        <v>43917</v>
-      </c>
-      <c r="G23" s="33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H23" s="33" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="I23" s="33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J23" s="33" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K23" s="33" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L23" s="33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M23" s="33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="N23" s="33" t="n">
-        <v>2.3</v>
-      </c>
+      <c r="A23" s="27" t="n"/>
+      <c r="B23" s="27" t="n"/>
+      <c r="C23" s="27" t="n"/>
+      <c r="D23" s="27" t="n"/>
+      <c r="E23" s="31" t="n"/>
+      <c r="F23" s="32" t="n"/>
+      <c r="G23" s="33" t="n"/>
+      <c r="H23" s="33" t="n"/>
+      <c r="I23" s="33" t="n"/>
+      <c r="J23" s="33" t="n"/>
+      <c r="K23" s="33" t="n"/>
+      <c r="L23" s="33" t="n"/>
+      <c r="M23" s="33" t="n"/>
+      <c r="N23" s="33" t="n"/>
       <c r="O23" s="34">
         <f>IF($A23="","",ROUND((PARAMETER!$C$5-F23)/365.25,1))</f>
         <v/>
@@ -3324,58 +3129,20 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="27" t="inlineStr">
-        <is>
-          <t>K-019</t>
-        </is>
-      </c>
-      <c r="B24" s="27" t="inlineStr">
-        <is>
-          <t>Zahra Permana</t>
-        </is>
-      </c>
-      <c r="C24" s="27" t="inlineStr">
-        <is>
-          <t>SDM</t>
-        </is>
-      </c>
-      <c r="D24" s="27" t="inlineStr">
-        <is>
-          <t>Spesialis</t>
-        </is>
-      </c>
-      <c r="E24" s="31" t="inlineStr">
-        <is>
-          <t>G6</t>
-        </is>
-      </c>
-      <c r="F24" s="32" t="n">
-        <v>43399</v>
-      </c>
-      <c r="G24" s="33" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H24" s="33" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="I24" s="33" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J24" s="33" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K24" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="L24" s="33" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="M24" s="33" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N24" s="33" t="n">
-        <v>3.1</v>
-      </c>
+      <c r="A24" s="27" t="n"/>
+      <c r="B24" s="27" t="n"/>
+      <c r="C24" s="27" t="n"/>
+      <c r="D24" s="27" t="n"/>
+      <c r="E24" s="31" t="n"/>
+      <c r="F24" s="32" t="n"/>
+      <c r="G24" s="33" t="n"/>
+      <c r="H24" s="33" t="n"/>
+      <c r="I24" s="33" t="n"/>
+      <c r="J24" s="33" t="n"/>
+      <c r="K24" s="33" t="n"/>
+      <c r="L24" s="33" t="n"/>
+      <c r="M24" s="33" t="n"/>
+      <c r="N24" s="33" t="n"/>
       <c r="O24" s="34">
         <f>IF($A24="","",ROUND((PARAMETER!$C$5-F24)/365.25,1))</f>
         <v/>
@@ -3414,58 +3181,20 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="27" t="inlineStr">
-        <is>
-          <t>K-020</t>
-        </is>
-      </c>
-      <c r="B25" s="27" t="inlineStr">
-        <is>
-          <t>Qori Setiawan</t>
-        </is>
-      </c>
-      <c r="C25" s="27" t="inlineStr">
-        <is>
-          <t>SDM</t>
-        </is>
-      </c>
-      <c r="D25" s="27" t="inlineStr">
-        <is>
-          <t>Senior Staf</t>
-        </is>
-      </c>
-      <c r="E25" s="31" t="inlineStr">
-        <is>
-          <t>G3</t>
-        </is>
-      </c>
-      <c r="F25" s="32" t="n">
-        <v>43352</v>
-      </c>
-      <c r="G25" s="33" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H25" s="33" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="I25" s="33" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J25" s="33" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K25" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="L25" s="33" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M25" s="33" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N25" s="33" t="n">
-        <v>4</v>
-      </c>
+      <c r="A25" s="27" t="n"/>
+      <c r="B25" s="27" t="n"/>
+      <c r="C25" s="27" t="n"/>
+      <c r="D25" s="27" t="n"/>
+      <c r="E25" s="31" t="n"/>
+      <c r="F25" s="32" t="n"/>
+      <c r="G25" s="33" t="n"/>
+      <c r="H25" s="33" t="n"/>
+      <c r="I25" s="33" t="n"/>
+      <c r="J25" s="33" t="n"/>
+      <c r="K25" s="33" t="n"/>
+      <c r="L25" s="33" t="n"/>
+      <c r="M25" s="33" t="n"/>
+      <c r="N25" s="33" t="n"/>
       <c r="O25" s="34">
         <f>IF($A25="","",ROUND((PARAMETER!$C$5-F25)/365.25,1))</f>
         <v/>
@@ -3503,1243 +3232,13 @@
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="27" t="inlineStr">
-        <is>
-          <t>K-021</t>
-        </is>
-      </c>
-      <c r="B26" s="27" t="inlineStr">
-        <is>
-          <t>Lina Permana</t>
-        </is>
-      </c>
-      <c r="C26" s="27" t="inlineStr">
-        <is>
-          <t>SDM</t>
-        </is>
-      </c>
-      <c r="D26" s="27" t="inlineStr">
-        <is>
-          <t>Staf</t>
-        </is>
-      </c>
-      <c r="E26" s="31" t="inlineStr">
-        <is>
-          <t>G4</t>
-        </is>
-      </c>
-      <c r="F26" s="32" t="n">
-        <v>45369</v>
-      </c>
-      <c r="G26" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="H26" s="33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I26" s="33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J26" s="33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K26" s="33" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L26" s="33" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="M26" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="N26" s="33" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O26" s="34">
-        <f>IF($A26="","",ROUND((PARAMETER!$C$5-F26)/365.25,1))</f>
-        <v/>
-      </c>
-      <c r="P26" s="35">
-        <f>IF($A26="","",SUMPRODUCT(I26:N26,PARAMETER!$C$11:$H$11)/SUM(PARAMETER!$C$11:$H$11))</f>
-        <v/>
-      </c>
-      <c r="Q26" s="35">
-        <f>IF($A26="","",SUMPRODUCT((PARAMETER!$C$12:$H$12-I26:N26&gt;0)*(PARAMETER!$C$12:$H$12-I26:N26))/6)</f>
-        <v/>
-      </c>
-      <c r="R26" s="26">
-        <f>IF($A26="","",IF(G26&gt;=PARAMETER!$C$6,3,IF(G26&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="S26" s="26">
-        <f>IF($A26="","",IF(H26&gt;=PARAMETER!$C$6,3,IF(H26&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="T26" s="26">
-        <f>IF($A26="","",(R26-1)*3+S26)</f>
-        <v/>
-      </c>
-      <c r="U26" s="36">
-        <f>IF($A26="","",INDEX(PARAMETER!$C$15:$C$23,T26))</f>
-        <v/>
-      </c>
-      <c r="V26" s="36">
-        <f>IF($A26="","",INDEX(PARAMETER!$C$10:$H$10,MATCH(MIN(I26:N26),I26:N26,0)))</f>
-        <v/>
-      </c>
-      <c r="W26" s="36">
-        <f>IF($A26="","",INDEX(PARAMETER!$E$15:$E$23,T26))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="27" t="inlineStr">
-        <is>
-          <t>K-022</t>
-        </is>
-      </c>
-      <c r="B27" s="27" t="inlineStr">
-        <is>
-          <t>Yusuf Kusuma</t>
-        </is>
-      </c>
-      <c r="C27" s="27" t="inlineStr">
-        <is>
-          <t>Operasional</t>
-        </is>
-      </c>
-      <c r="D27" s="27" t="inlineStr">
-        <is>
-          <t>Spesialis</t>
-        </is>
-      </c>
-      <c r="E27" s="31" t="inlineStr">
-        <is>
-          <t>G4</t>
-        </is>
-      </c>
-      <c r="F27" s="32" t="n">
-        <v>43310</v>
-      </c>
-      <c r="G27" s="33" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H27" s="33" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I27" s="33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J27" s="33" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K27" s="33" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L27" s="33" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="M27" s="33" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N27" s="33" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O27" s="34">
-        <f>IF($A27="","",ROUND((PARAMETER!$C$5-F27)/365.25,1))</f>
-        <v/>
-      </c>
-      <c r="P27" s="35">
-        <f>IF($A27="","",SUMPRODUCT(I27:N27,PARAMETER!$C$11:$H$11)/SUM(PARAMETER!$C$11:$H$11))</f>
-        <v/>
-      </c>
-      <c r="Q27" s="35">
-        <f>IF($A27="","",SUMPRODUCT((PARAMETER!$C$12:$H$12-I27:N27&gt;0)*(PARAMETER!$C$12:$H$12-I27:N27))/6)</f>
-        <v/>
-      </c>
-      <c r="R27" s="26">
-        <f>IF($A27="","",IF(G27&gt;=PARAMETER!$C$6,3,IF(G27&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="S27" s="26">
-        <f>IF($A27="","",IF(H27&gt;=PARAMETER!$C$6,3,IF(H27&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="T27" s="26">
-        <f>IF($A27="","",(R27-1)*3+S27)</f>
-        <v/>
-      </c>
-      <c r="U27" s="36">
-        <f>IF($A27="","",INDEX(PARAMETER!$C$15:$C$23,T27))</f>
-        <v/>
-      </c>
-      <c r="V27" s="36">
-        <f>IF($A27="","",INDEX(PARAMETER!$C$10:$H$10,MATCH(MIN(I27:N27),I27:N27,0)))</f>
-        <v/>
-      </c>
-      <c r="W27" s="36">
-        <f>IF($A27="","",INDEX(PARAMETER!$E$15:$E$23,T27))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="27" t="inlineStr">
-        <is>
-          <t>K-023</t>
-        </is>
-      </c>
-      <c r="B28" s="27" t="inlineStr">
-        <is>
-          <t>Yusuf Saputra</t>
-        </is>
-      </c>
-      <c r="C28" s="27" t="inlineStr">
-        <is>
-          <t>Keuangan</t>
-        </is>
-      </c>
-      <c r="D28" s="27" t="inlineStr">
-        <is>
-          <t>Spesialis</t>
-        </is>
-      </c>
-      <c r="E28" s="31" t="inlineStr">
-        <is>
-          <t>G6</t>
-        </is>
-      </c>
-      <c r="F28" s="32" t="n">
-        <v>43864</v>
-      </c>
-      <c r="G28" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="H28" s="33" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I28" s="33" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J28" s="33" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K28" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="L28" s="33" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="M28" s="33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N28" s="33" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O28" s="34">
-        <f>IF($A28="","",ROUND((PARAMETER!$C$5-F28)/365.25,1))</f>
-        <v/>
-      </c>
-      <c r="P28" s="35">
-        <f>IF($A28="","",SUMPRODUCT(I28:N28,PARAMETER!$C$11:$H$11)/SUM(PARAMETER!$C$11:$H$11))</f>
-        <v/>
-      </c>
-      <c r="Q28" s="35">
-        <f>IF($A28="","",SUMPRODUCT((PARAMETER!$C$12:$H$12-I28:N28&gt;0)*(PARAMETER!$C$12:$H$12-I28:N28))/6)</f>
-        <v/>
-      </c>
-      <c r="R28" s="26">
-        <f>IF($A28="","",IF(G28&gt;=PARAMETER!$C$6,3,IF(G28&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="S28" s="26">
-        <f>IF($A28="","",IF(H28&gt;=PARAMETER!$C$6,3,IF(H28&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="T28" s="26">
-        <f>IF($A28="","",(R28-1)*3+S28)</f>
-        <v/>
-      </c>
-      <c r="U28" s="36">
-        <f>IF($A28="","",INDEX(PARAMETER!$C$15:$C$23,T28))</f>
-        <v/>
-      </c>
-      <c r="V28" s="36">
-        <f>IF($A28="","",INDEX(PARAMETER!$C$10:$H$10,MATCH(MIN(I28:N28),I28:N28,0)))</f>
-        <v/>
-      </c>
-      <c r="W28" s="36">
-        <f>IF($A28="","",INDEX(PARAMETER!$E$15:$E$23,T28))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="27" t="inlineStr">
-        <is>
-          <t>K-024</t>
-        </is>
-      </c>
-      <c r="B29" s="27" t="inlineStr">
-        <is>
-          <t>Yusuf Hidayat</t>
-        </is>
-      </c>
-      <c r="C29" s="27" t="inlineStr">
-        <is>
-          <t>Keuangan</t>
-        </is>
-      </c>
-      <c r="D29" s="27" t="inlineStr">
-        <is>
-          <t>Supervisor</t>
-        </is>
-      </c>
-      <c r="E29" s="31" t="inlineStr">
-        <is>
-          <t>G3</t>
-        </is>
-      </c>
-      <c r="F29" s="32" t="n">
-        <v>44731</v>
-      </c>
-      <c r="G29" s="33" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H29" s="33" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="I29" s="33" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J29" s="33" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="K29" s="33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L29" s="33" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="M29" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="N29" s="33" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O29" s="34">
-        <f>IF($A29="","",ROUND((PARAMETER!$C$5-F29)/365.25,1))</f>
-        <v/>
-      </c>
-      <c r="P29" s="35">
-        <f>IF($A29="","",SUMPRODUCT(I29:N29,PARAMETER!$C$11:$H$11)/SUM(PARAMETER!$C$11:$H$11))</f>
-        <v/>
-      </c>
-      <c r="Q29" s="35">
-        <f>IF($A29="","",SUMPRODUCT((PARAMETER!$C$12:$H$12-I29:N29&gt;0)*(PARAMETER!$C$12:$H$12-I29:N29))/6)</f>
-        <v/>
-      </c>
-      <c r="R29" s="26">
-        <f>IF($A29="","",IF(G29&gt;=PARAMETER!$C$6,3,IF(G29&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="S29" s="26">
-        <f>IF($A29="","",IF(H29&gt;=PARAMETER!$C$6,3,IF(H29&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="T29" s="26">
-        <f>IF($A29="","",(R29-1)*3+S29)</f>
-        <v/>
-      </c>
-      <c r="U29" s="36">
-        <f>IF($A29="","",INDEX(PARAMETER!$C$15:$C$23,T29))</f>
-        <v/>
-      </c>
-      <c r="V29" s="36">
-        <f>IF($A29="","",INDEX(PARAMETER!$C$10:$H$10,MATCH(MIN(I29:N29),I29:N29,0)))</f>
-        <v/>
-      </c>
-      <c r="W29" s="36">
-        <f>IF($A29="","",INDEX(PARAMETER!$E$15:$E$23,T29))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="27" t="inlineStr">
-        <is>
-          <t>K-025</t>
-        </is>
-      </c>
-      <c r="B30" s="27" t="inlineStr">
-        <is>
-          <t>Dian Pratama</t>
-        </is>
-      </c>
-      <c r="C30" s="27" t="inlineStr">
-        <is>
-          <t>Operasional</t>
-        </is>
-      </c>
-      <c r="D30" s="27" t="inlineStr">
-        <is>
-          <t>Supervisor</t>
-        </is>
-      </c>
-      <c r="E30" s="31" t="inlineStr">
-        <is>
-          <t>G6</t>
-        </is>
-      </c>
-      <c r="F30" s="32" t="n">
-        <v>44931</v>
-      </c>
-      <c r="G30" s="33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H30" s="33" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I30" s="33" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J30" s="33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K30" s="33" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L30" s="33" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="M30" s="33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N30" s="33" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O30" s="34">
-        <f>IF($A30="","",ROUND((PARAMETER!$C$5-F30)/365.25,1))</f>
-        <v/>
-      </c>
-      <c r="P30" s="35">
-        <f>IF($A30="","",SUMPRODUCT(I30:N30,PARAMETER!$C$11:$H$11)/SUM(PARAMETER!$C$11:$H$11))</f>
-        <v/>
-      </c>
-      <c r="Q30" s="35">
-        <f>IF($A30="","",SUMPRODUCT((PARAMETER!$C$12:$H$12-I30:N30&gt;0)*(PARAMETER!$C$12:$H$12-I30:N30))/6)</f>
-        <v/>
-      </c>
-      <c r="R30" s="26">
-        <f>IF($A30="","",IF(G30&gt;=PARAMETER!$C$6,3,IF(G30&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="S30" s="26">
-        <f>IF($A30="","",IF(H30&gt;=PARAMETER!$C$6,3,IF(H30&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="T30" s="26">
-        <f>IF($A30="","",(R30-1)*3+S30)</f>
-        <v/>
-      </c>
-      <c r="U30" s="36">
-        <f>IF($A30="","",INDEX(PARAMETER!$C$15:$C$23,T30))</f>
-        <v/>
-      </c>
-      <c r="V30" s="36">
-        <f>IF($A30="","",INDEX(PARAMETER!$C$10:$H$10,MATCH(MIN(I30:N30),I30:N30,0)))</f>
-        <v/>
-      </c>
-      <c r="W30" s="36">
-        <f>IF($A30="","",INDEX(PARAMETER!$E$15:$E$23,T30))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="27" t="n"/>
-      <c r="B31" s="27" t="n"/>
-      <c r="C31" s="27" t="n"/>
-      <c r="D31" s="27" t="n"/>
-      <c r="E31" s="31" t="n"/>
-      <c r="F31" s="32" t="n"/>
-      <c r="G31" s="33" t="n"/>
-      <c r="H31" s="33" t="n"/>
-      <c r="I31" s="33" t="n"/>
-      <c r="J31" s="33" t="n"/>
-      <c r="K31" s="33" t="n"/>
-      <c r="L31" s="33" t="n"/>
-      <c r="M31" s="33" t="n"/>
-      <c r="N31" s="33" t="n"/>
-      <c r="O31" s="34">
-        <f>IF($A31="","",ROUND((PARAMETER!$C$5-F31)/365.25,1))</f>
-        <v/>
-      </c>
-      <c r="P31" s="35">
-        <f>IF($A31="","",SUMPRODUCT(I31:N31,PARAMETER!$C$11:$H$11)/SUM(PARAMETER!$C$11:$H$11))</f>
-        <v/>
-      </c>
-      <c r="Q31" s="35">
-        <f>IF($A31="","",SUMPRODUCT((PARAMETER!$C$12:$H$12-I31:N31&gt;0)*(PARAMETER!$C$12:$H$12-I31:N31))/6)</f>
-        <v/>
-      </c>
-      <c r="R31" s="26">
-        <f>IF($A31="","",IF(G31&gt;=PARAMETER!$C$6,3,IF(G31&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="S31" s="26">
-        <f>IF($A31="","",IF(H31&gt;=PARAMETER!$C$6,3,IF(H31&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="T31" s="26">
-        <f>IF($A31="","",(R31-1)*3+S31)</f>
-        <v/>
-      </c>
-      <c r="U31" s="36">
-        <f>IF($A31="","",INDEX(PARAMETER!$C$15:$C$23,T31))</f>
-        <v/>
-      </c>
-      <c r="V31" s="36">
-        <f>IF($A31="","",INDEX(PARAMETER!$C$10:$H$10,MATCH(MIN(I31:N31),I31:N31,0)))</f>
-        <v/>
-      </c>
-      <c r="W31" s="36">
-        <f>IF($A31="","",INDEX(PARAMETER!$E$15:$E$23,T31))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="27" t="n"/>
-      <c r="B32" s="27" t="n"/>
-      <c r="C32" s="27" t="n"/>
-      <c r="D32" s="27" t="n"/>
-      <c r="E32" s="31" t="n"/>
-      <c r="F32" s="32" t="n"/>
-      <c r="G32" s="33" t="n"/>
-      <c r="H32" s="33" t="n"/>
-      <c r="I32" s="33" t="n"/>
-      <c r="J32" s="33" t="n"/>
-      <c r="K32" s="33" t="n"/>
-      <c r="L32" s="33" t="n"/>
-      <c r="M32" s="33" t="n"/>
-      <c r="N32" s="33" t="n"/>
-      <c r="O32" s="34">
-        <f>IF($A32="","",ROUND((PARAMETER!$C$5-F32)/365.25,1))</f>
-        <v/>
-      </c>
-      <c r="P32" s="35">
-        <f>IF($A32="","",SUMPRODUCT(I32:N32,PARAMETER!$C$11:$H$11)/SUM(PARAMETER!$C$11:$H$11))</f>
-        <v/>
-      </c>
-      <c r="Q32" s="35">
-        <f>IF($A32="","",SUMPRODUCT((PARAMETER!$C$12:$H$12-I32:N32&gt;0)*(PARAMETER!$C$12:$H$12-I32:N32))/6)</f>
-        <v/>
-      </c>
-      <c r="R32" s="26">
-        <f>IF($A32="","",IF(G32&gt;=PARAMETER!$C$6,3,IF(G32&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="S32" s="26">
-        <f>IF($A32="","",IF(H32&gt;=PARAMETER!$C$6,3,IF(H32&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="T32" s="26">
-        <f>IF($A32="","",(R32-1)*3+S32)</f>
-        <v/>
-      </c>
-      <c r="U32" s="36">
-        <f>IF($A32="","",INDEX(PARAMETER!$C$15:$C$23,T32))</f>
-        <v/>
-      </c>
-      <c r="V32" s="36">
-        <f>IF($A32="","",INDEX(PARAMETER!$C$10:$H$10,MATCH(MIN(I32:N32),I32:N32,0)))</f>
-        <v/>
-      </c>
-      <c r="W32" s="36">
-        <f>IF($A32="","",INDEX(PARAMETER!$E$15:$E$23,T32))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="27" t="n"/>
-      <c r="B33" s="27" t="n"/>
-      <c r="C33" s="27" t="n"/>
-      <c r="D33" s="27" t="n"/>
-      <c r="E33" s="31" t="n"/>
-      <c r="F33" s="32" t="n"/>
-      <c r="G33" s="33" t="n"/>
-      <c r="H33" s="33" t="n"/>
-      <c r="I33" s="33" t="n"/>
-      <c r="J33" s="33" t="n"/>
-      <c r="K33" s="33" t="n"/>
-      <c r="L33" s="33" t="n"/>
-      <c r="M33" s="33" t="n"/>
-      <c r="N33" s="33" t="n"/>
-      <c r="O33" s="34">
-        <f>IF($A33="","",ROUND((PARAMETER!$C$5-F33)/365.25,1))</f>
-        <v/>
-      </c>
-      <c r="P33" s="35">
-        <f>IF($A33="","",SUMPRODUCT(I33:N33,PARAMETER!$C$11:$H$11)/SUM(PARAMETER!$C$11:$H$11))</f>
-        <v/>
-      </c>
-      <c r="Q33" s="35">
-        <f>IF($A33="","",SUMPRODUCT((PARAMETER!$C$12:$H$12-I33:N33&gt;0)*(PARAMETER!$C$12:$H$12-I33:N33))/6)</f>
-        <v/>
-      </c>
-      <c r="R33" s="26">
-        <f>IF($A33="","",IF(G33&gt;=PARAMETER!$C$6,3,IF(G33&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="S33" s="26">
-        <f>IF($A33="","",IF(H33&gt;=PARAMETER!$C$6,3,IF(H33&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="T33" s="26">
-        <f>IF($A33="","",(R33-1)*3+S33)</f>
-        <v/>
-      </c>
-      <c r="U33" s="36">
-        <f>IF($A33="","",INDEX(PARAMETER!$C$15:$C$23,T33))</f>
-        <v/>
-      </c>
-      <c r="V33" s="36">
-        <f>IF($A33="","",INDEX(PARAMETER!$C$10:$H$10,MATCH(MIN(I33:N33),I33:N33,0)))</f>
-        <v/>
-      </c>
-      <c r="W33" s="36">
-        <f>IF($A33="","",INDEX(PARAMETER!$E$15:$E$23,T33))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="27" t="n"/>
-      <c r="B34" s="27" t="n"/>
-      <c r="C34" s="27" t="n"/>
-      <c r="D34" s="27" t="n"/>
-      <c r="E34" s="31" t="n"/>
-      <c r="F34" s="32" t="n"/>
-      <c r="G34" s="33" t="n"/>
-      <c r="H34" s="33" t="n"/>
-      <c r="I34" s="33" t="n"/>
-      <c r="J34" s="33" t="n"/>
-      <c r="K34" s="33" t="n"/>
-      <c r="L34" s="33" t="n"/>
-      <c r="M34" s="33" t="n"/>
-      <c r="N34" s="33" t="n"/>
-      <c r="O34" s="34">
-        <f>IF($A34="","",ROUND((PARAMETER!$C$5-F34)/365.25,1))</f>
-        <v/>
-      </c>
-      <c r="P34" s="35">
-        <f>IF($A34="","",SUMPRODUCT(I34:N34,PARAMETER!$C$11:$H$11)/SUM(PARAMETER!$C$11:$H$11))</f>
-        <v/>
-      </c>
-      <c r="Q34" s="35">
-        <f>IF($A34="","",SUMPRODUCT((PARAMETER!$C$12:$H$12-I34:N34&gt;0)*(PARAMETER!$C$12:$H$12-I34:N34))/6)</f>
-        <v/>
-      </c>
-      <c r="R34" s="26">
-        <f>IF($A34="","",IF(G34&gt;=PARAMETER!$C$6,3,IF(G34&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="S34" s="26">
-        <f>IF($A34="","",IF(H34&gt;=PARAMETER!$C$6,3,IF(H34&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="T34" s="26">
-        <f>IF($A34="","",(R34-1)*3+S34)</f>
-        <v/>
-      </c>
-      <c r="U34" s="36">
-        <f>IF($A34="","",INDEX(PARAMETER!$C$15:$C$23,T34))</f>
-        <v/>
-      </c>
-      <c r="V34" s="36">
-        <f>IF($A34="","",INDEX(PARAMETER!$C$10:$H$10,MATCH(MIN(I34:N34),I34:N34,0)))</f>
-        <v/>
-      </c>
-      <c r="W34" s="36">
-        <f>IF($A34="","",INDEX(PARAMETER!$E$15:$E$23,T34))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="27" t="n"/>
-      <c r="B35" s="27" t="n"/>
-      <c r="C35" s="27" t="n"/>
-      <c r="D35" s="27" t="n"/>
-      <c r="E35" s="31" t="n"/>
-      <c r="F35" s="32" t="n"/>
-      <c r="G35" s="33" t="n"/>
-      <c r="H35" s="33" t="n"/>
-      <c r="I35" s="33" t="n"/>
-      <c r="J35" s="33" t="n"/>
-      <c r="K35" s="33" t="n"/>
-      <c r="L35" s="33" t="n"/>
-      <c r="M35" s="33" t="n"/>
-      <c r="N35" s="33" t="n"/>
-      <c r="O35" s="34">
-        <f>IF($A35="","",ROUND((PARAMETER!$C$5-F35)/365.25,1))</f>
-        <v/>
-      </c>
-      <c r="P35" s="35">
-        <f>IF($A35="","",SUMPRODUCT(I35:N35,PARAMETER!$C$11:$H$11)/SUM(PARAMETER!$C$11:$H$11))</f>
-        <v/>
-      </c>
-      <c r="Q35" s="35">
-        <f>IF($A35="","",SUMPRODUCT((PARAMETER!$C$12:$H$12-I35:N35&gt;0)*(PARAMETER!$C$12:$H$12-I35:N35))/6)</f>
-        <v/>
-      </c>
-      <c r="R35" s="26">
-        <f>IF($A35="","",IF(G35&gt;=PARAMETER!$C$6,3,IF(G35&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="S35" s="26">
-        <f>IF($A35="","",IF(H35&gt;=PARAMETER!$C$6,3,IF(H35&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="T35" s="26">
-        <f>IF($A35="","",(R35-1)*3+S35)</f>
-        <v/>
-      </c>
-      <c r="U35" s="36">
-        <f>IF($A35="","",INDEX(PARAMETER!$C$15:$C$23,T35))</f>
-        <v/>
-      </c>
-      <c r="V35" s="36">
-        <f>IF($A35="","",INDEX(PARAMETER!$C$10:$H$10,MATCH(MIN(I35:N35),I35:N35,0)))</f>
-        <v/>
-      </c>
-      <c r="W35" s="36">
-        <f>IF($A35="","",INDEX(PARAMETER!$E$15:$E$23,T35))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="27" t="n"/>
-      <c r="B36" s="27" t="n"/>
-      <c r="C36" s="27" t="n"/>
-      <c r="D36" s="27" t="n"/>
-      <c r="E36" s="31" t="n"/>
-      <c r="F36" s="32" t="n"/>
-      <c r="G36" s="33" t="n"/>
-      <c r="H36" s="33" t="n"/>
-      <c r="I36" s="33" t="n"/>
-      <c r="J36" s="33" t="n"/>
-      <c r="K36" s="33" t="n"/>
-      <c r="L36" s="33" t="n"/>
-      <c r="M36" s="33" t="n"/>
-      <c r="N36" s="33" t="n"/>
-      <c r="O36" s="34">
-        <f>IF($A36="","",ROUND((PARAMETER!$C$5-F36)/365.25,1))</f>
-        <v/>
-      </c>
-      <c r="P36" s="35">
-        <f>IF($A36="","",SUMPRODUCT(I36:N36,PARAMETER!$C$11:$H$11)/SUM(PARAMETER!$C$11:$H$11))</f>
-        <v/>
-      </c>
-      <c r="Q36" s="35">
-        <f>IF($A36="","",SUMPRODUCT((PARAMETER!$C$12:$H$12-I36:N36&gt;0)*(PARAMETER!$C$12:$H$12-I36:N36))/6)</f>
-        <v/>
-      </c>
-      <c r="R36" s="26">
-        <f>IF($A36="","",IF(G36&gt;=PARAMETER!$C$6,3,IF(G36&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="S36" s="26">
-        <f>IF($A36="","",IF(H36&gt;=PARAMETER!$C$6,3,IF(H36&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="T36" s="26">
-        <f>IF($A36="","",(R36-1)*3+S36)</f>
-        <v/>
-      </c>
-      <c r="U36" s="36">
-        <f>IF($A36="","",INDEX(PARAMETER!$C$15:$C$23,T36))</f>
-        <v/>
-      </c>
-      <c r="V36" s="36">
-        <f>IF($A36="","",INDEX(PARAMETER!$C$10:$H$10,MATCH(MIN(I36:N36),I36:N36,0)))</f>
-        <v/>
-      </c>
-      <c r="W36" s="36">
-        <f>IF($A36="","",INDEX(PARAMETER!$E$15:$E$23,T36))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="27" t="n"/>
-      <c r="B37" s="27" t="n"/>
-      <c r="C37" s="27" t="n"/>
-      <c r="D37" s="27" t="n"/>
-      <c r="E37" s="31" t="n"/>
-      <c r="F37" s="32" t="n"/>
-      <c r="G37" s="33" t="n"/>
-      <c r="H37" s="33" t="n"/>
-      <c r="I37" s="33" t="n"/>
-      <c r="J37" s="33" t="n"/>
-      <c r="K37" s="33" t="n"/>
-      <c r="L37" s="33" t="n"/>
-      <c r="M37" s="33" t="n"/>
-      <c r="N37" s="33" t="n"/>
-      <c r="O37" s="34">
-        <f>IF($A37="","",ROUND((PARAMETER!$C$5-F37)/365.25,1))</f>
-        <v/>
-      </c>
-      <c r="P37" s="35">
-        <f>IF($A37="","",SUMPRODUCT(I37:N37,PARAMETER!$C$11:$H$11)/SUM(PARAMETER!$C$11:$H$11))</f>
-        <v/>
-      </c>
-      <c r="Q37" s="35">
-        <f>IF($A37="","",SUMPRODUCT((PARAMETER!$C$12:$H$12-I37:N37&gt;0)*(PARAMETER!$C$12:$H$12-I37:N37))/6)</f>
-        <v/>
-      </c>
-      <c r="R37" s="26">
-        <f>IF($A37="","",IF(G37&gt;=PARAMETER!$C$6,3,IF(G37&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="S37" s="26">
-        <f>IF($A37="","",IF(H37&gt;=PARAMETER!$C$6,3,IF(H37&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="T37" s="26">
-        <f>IF($A37="","",(R37-1)*3+S37)</f>
-        <v/>
-      </c>
-      <c r="U37" s="36">
-        <f>IF($A37="","",INDEX(PARAMETER!$C$15:$C$23,T37))</f>
-        <v/>
-      </c>
-      <c r="V37" s="36">
-        <f>IF($A37="","",INDEX(PARAMETER!$C$10:$H$10,MATCH(MIN(I37:N37),I37:N37,0)))</f>
-        <v/>
-      </c>
-      <c r="W37" s="36">
-        <f>IF($A37="","",INDEX(PARAMETER!$E$15:$E$23,T37))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="27" t="n"/>
-      <c r="B38" s="27" t="n"/>
-      <c r="C38" s="27" t="n"/>
-      <c r="D38" s="27" t="n"/>
-      <c r="E38" s="31" t="n"/>
-      <c r="F38" s="32" t="n"/>
-      <c r="G38" s="33" t="n"/>
-      <c r="H38" s="33" t="n"/>
-      <c r="I38" s="33" t="n"/>
-      <c r="J38" s="33" t="n"/>
-      <c r="K38" s="33" t="n"/>
-      <c r="L38" s="33" t="n"/>
-      <c r="M38" s="33" t="n"/>
-      <c r="N38" s="33" t="n"/>
-      <c r="O38" s="34">
-        <f>IF($A38="","",ROUND((PARAMETER!$C$5-F38)/365.25,1))</f>
-        <v/>
-      </c>
-      <c r="P38" s="35">
-        <f>IF($A38="","",SUMPRODUCT(I38:N38,PARAMETER!$C$11:$H$11)/SUM(PARAMETER!$C$11:$H$11))</f>
-        <v/>
-      </c>
-      <c r="Q38" s="35">
-        <f>IF($A38="","",SUMPRODUCT((PARAMETER!$C$12:$H$12-I38:N38&gt;0)*(PARAMETER!$C$12:$H$12-I38:N38))/6)</f>
-        <v/>
-      </c>
-      <c r="R38" s="26">
-        <f>IF($A38="","",IF(G38&gt;=PARAMETER!$C$6,3,IF(G38&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="S38" s="26">
-        <f>IF($A38="","",IF(H38&gt;=PARAMETER!$C$6,3,IF(H38&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="T38" s="26">
-        <f>IF($A38="","",(R38-1)*3+S38)</f>
-        <v/>
-      </c>
-      <c r="U38" s="36">
-        <f>IF($A38="","",INDEX(PARAMETER!$C$15:$C$23,T38))</f>
-        <v/>
-      </c>
-      <c r="V38" s="36">
-        <f>IF($A38="","",INDEX(PARAMETER!$C$10:$H$10,MATCH(MIN(I38:N38),I38:N38,0)))</f>
-        <v/>
-      </c>
-      <c r="W38" s="36">
-        <f>IF($A38="","",INDEX(PARAMETER!$E$15:$E$23,T38))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="27" t="n"/>
-      <c r="B39" s="27" t="n"/>
-      <c r="C39" s="27" t="n"/>
-      <c r="D39" s="27" t="n"/>
-      <c r="E39" s="31" t="n"/>
-      <c r="F39" s="32" t="n"/>
-      <c r="G39" s="33" t="n"/>
-      <c r="H39" s="33" t="n"/>
-      <c r="I39" s="33" t="n"/>
-      <c r="J39" s="33" t="n"/>
-      <c r="K39" s="33" t="n"/>
-      <c r="L39" s="33" t="n"/>
-      <c r="M39" s="33" t="n"/>
-      <c r="N39" s="33" t="n"/>
-      <c r="O39" s="34">
-        <f>IF($A39="","",ROUND((PARAMETER!$C$5-F39)/365.25,1))</f>
-        <v/>
-      </c>
-      <c r="P39" s="35">
-        <f>IF($A39="","",SUMPRODUCT(I39:N39,PARAMETER!$C$11:$H$11)/SUM(PARAMETER!$C$11:$H$11))</f>
-        <v/>
-      </c>
-      <c r="Q39" s="35">
-        <f>IF($A39="","",SUMPRODUCT((PARAMETER!$C$12:$H$12-I39:N39&gt;0)*(PARAMETER!$C$12:$H$12-I39:N39))/6)</f>
-        <v/>
-      </c>
-      <c r="R39" s="26">
-        <f>IF($A39="","",IF(G39&gt;=PARAMETER!$C$6,3,IF(G39&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="S39" s="26">
-        <f>IF($A39="","",IF(H39&gt;=PARAMETER!$C$6,3,IF(H39&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="T39" s="26">
-        <f>IF($A39="","",(R39-1)*3+S39)</f>
-        <v/>
-      </c>
-      <c r="U39" s="36">
-        <f>IF($A39="","",INDEX(PARAMETER!$C$15:$C$23,T39))</f>
-        <v/>
-      </c>
-      <c r="V39" s="36">
-        <f>IF($A39="","",INDEX(PARAMETER!$C$10:$H$10,MATCH(MIN(I39:N39),I39:N39,0)))</f>
-        <v/>
-      </c>
-      <c r="W39" s="36">
-        <f>IF($A39="","",INDEX(PARAMETER!$E$15:$E$23,T39))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="27" t="n"/>
-      <c r="B40" s="27" t="n"/>
-      <c r="C40" s="27" t="n"/>
-      <c r="D40" s="27" t="n"/>
-      <c r="E40" s="31" t="n"/>
-      <c r="F40" s="32" t="n"/>
-      <c r="G40" s="33" t="n"/>
-      <c r="H40" s="33" t="n"/>
-      <c r="I40" s="33" t="n"/>
-      <c r="J40" s="33" t="n"/>
-      <c r="K40" s="33" t="n"/>
-      <c r="L40" s="33" t="n"/>
-      <c r="M40" s="33" t="n"/>
-      <c r="N40" s="33" t="n"/>
-      <c r="O40" s="34">
-        <f>IF($A40="","",ROUND((PARAMETER!$C$5-F40)/365.25,1))</f>
-        <v/>
-      </c>
-      <c r="P40" s="35">
-        <f>IF($A40="","",SUMPRODUCT(I40:N40,PARAMETER!$C$11:$H$11)/SUM(PARAMETER!$C$11:$H$11))</f>
-        <v/>
-      </c>
-      <c r="Q40" s="35">
-        <f>IF($A40="","",SUMPRODUCT((PARAMETER!$C$12:$H$12-I40:N40&gt;0)*(PARAMETER!$C$12:$H$12-I40:N40))/6)</f>
-        <v/>
-      </c>
-      <c r="R40" s="26">
-        <f>IF($A40="","",IF(G40&gt;=PARAMETER!$C$6,3,IF(G40&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="S40" s="26">
-        <f>IF($A40="","",IF(H40&gt;=PARAMETER!$C$6,3,IF(H40&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="T40" s="26">
-        <f>IF($A40="","",(R40-1)*3+S40)</f>
-        <v/>
-      </c>
-      <c r="U40" s="36">
-        <f>IF($A40="","",INDEX(PARAMETER!$C$15:$C$23,T40))</f>
-        <v/>
-      </c>
-      <c r="V40" s="36">
-        <f>IF($A40="","",INDEX(PARAMETER!$C$10:$H$10,MATCH(MIN(I40:N40),I40:N40,0)))</f>
-        <v/>
-      </c>
-      <c r="W40" s="36">
-        <f>IF($A40="","",INDEX(PARAMETER!$E$15:$E$23,T40))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="27" t="n"/>
-      <c r="B41" s="27" t="n"/>
-      <c r="C41" s="27" t="n"/>
-      <c r="D41" s="27" t="n"/>
-      <c r="E41" s="31" t="n"/>
-      <c r="F41" s="32" t="n"/>
-      <c r="G41" s="33" t="n"/>
-      <c r="H41" s="33" t="n"/>
-      <c r="I41" s="33" t="n"/>
-      <c r="J41" s="33" t="n"/>
-      <c r="K41" s="33" t="n"/>
-      <c r="L41" s="33" t="n"/>
-      <c r="M41" s="33" t="n"/>
-      <c r="N41" s="33" t="n"/>
-      <c r="O41" s="34">
-        <f>IF($A41="","",ROUND((PARAMETER!$C$5-F41)/365.25,1))</f>
-        <v/>
-      </c>
-      <c r="P41" s="35">
-        <f>IF($A41="","",SUMPRODUCT(I41:N41,PARAMETER!$C$11:$H$11)/SUM(PARAMETER!$C$11:$H$11))</f>
-        <v/>
-      </c>
-      <c r="Q41" s="35">
-        <f>IF($A41="","",SUMPRODUCT((PARAMETER!$C$12:$H$12-I41:N41&gt;0)*(PARAMETER!$C$12:$H$12-I41:N41))/6)</f>
-        <v/>
-      </c>
-      <c r="R41" s="26">
-        <f>IF($A41="","",IF(G41&gt;=PARAMETER!$C$6,3,IF(G41&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="S41" s="26">
-        <f>IF($A41="","",IF(H41&gt;=PARAMETER!$C$6,3,IF(H41&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="T41" s="26">
-        <f>IF($A41="","",(R41-1)*3+S41)</f>
-        <v/>
-      </c>
-      <c r="U41" s="36">
-        <f>IF($A41="","",INDEX(PARAMETER!$C$15:$C$23,T41))</f>
-        <v/>
-      </c>
-      <c r="V41" s="36">
-        <f>IF($A41="","",INDEX(PARAMETER!$C$10:$H$10,MATCH(MIN(I41:N41),I41:N41,0)))</f>
-        <v/>
-      </c>
-      <c r="W41" s="36">
-        <f>IF($A41="","",INDEX(PARAMETER!$E$15:$E$23,T41))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="27" t="n"/>
-      <c r="B42" s="27" t="n"/>
-      <c r="C42" s="27" t="n"/>
-      <c r="D42" s="27" t="n"/>
-      <c r="E42" s="31" t="n"/>
-      <c r="F42" s="32" t="n"/>
-      <c r="G42" s="33" t="n"/>
-      <c r="H42" s="33" t="n"/>
-      <c r="I42" s="33" t="n"/>
-      <c r="J42" s="33" t="n"/>
-      <c r="K42" s="33" t="n"/>
-      <c r="L42" s="33" t="n"/>
-      <c r="M42" s="33" t="n"/>
-      <c r="N42" s="33" t="n"/>
-      <c r="O42" s="34">
-        <f>IF($A42="","",ROUND((PARAMETER!$C$5-F42)/365.25,1))</f>
-        <v/>
-      </c>
-      <c r="P42" s="35">
-        <f>IF($A42="","",SUMPRODUCT(I42:N42,PARAMETER!$C$11:$H$11)/SUM(PARAMETER!$C$11:$H$11))</f>
-        <v/>
-      </c>
-      <c r="Q42" s="35">
-        <f>IF($A42="","",SUMPRODUCT((PARAMETER!$C$12:$H$12-I42:N42&gt;0)*(PARAMETER!$C$12:$H$12-I42:N42))/6)</f>
-        <v/>
-      </c>
-      <c r="R42" s="26">
-        <f>IF($A42="","",IF(G42&gt;=PARAMETER!$C$6,3,IF(G42&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="S42" s="26">
-        <f>IF($A42="","",IF(H42&gt;=PARAMETER!$C$6,3,IF(H42&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="T42" s="26">
-        <f>IF($A42="","",(R42-1)*3+S42)</f>
-        <v/>
-      </c>
-      <c r="U42" s="36">
-        <f>IF($A42="","",INDEX(PARAMETER!$C$15:$C$23,T42))</f>
-        <v/>
-      </c>
-      <c r="V42" s="36">
-        <f>IF($A42="","",INDEX(PARAMETER!$C$10:$H$10,MATCH(MIN(I42:N42),I42:N42,0)))</f>
-        <v/>
-      </c>
-      <c r="W42" s="36">
-        <f>IF($A42="","",INDEX(PARAMETER!$E$15:$E$23,T42))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="27" t="n"/>
-      <c r="B43" s="27" t="n"/>
-      <c r="C43" s="27" t="n"/>
-      <c r="D43" s="27" t="n"/>
-      <c r="E43" s="31" t="n"/>
-      <c r="F43" s="32" t="n"/>
-      <c r="G43" s="33" t="n"/>
-      <c r="H43" s="33" t="n"/>
-      <c r="I43" s="33" t="n"/>
-      <c r="J43" s="33" t="n"/>
-      <c r="K43" s="33" t="n"/>
-      <c r="L43" s="33" t="n"/>
-      <c r="M43" s="33" t="n"/>
-      <c r="N43" s="33" t="n"/>
-      <c r="O43" s="34">
-        <f>IF($A43="","",ROUND((PARAMETER!$C$5-F43)/365.25,1))</f>
-        <v/>
-      </c>
-      <c r="P43" s="35">
-        <f>IF($A43="","",SUMPRODUCT(I43:N43,PARAMETER!$C$11:$H$11)/SUM(PARAMETER!$C$11:$H$11))</f>
-        <v/>
-      </c>
-      <c r="Q43" s="35">
-        <f>IF($A43="","",SUMPRODUCT((PARAMETER!$C$12:$H$12-I43:N43&gt;0)*(PARAMETER!$C$12:$H$12-I43:N43))/6)</f>
-        <v/>
-      </c>
-      <c r="R43" s="26">
-        <f>IF($A43="","",IF(G43&gt;=PARAMETER!$C$6,3,IF(G43&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="S43" s="26">
-        <f>IF($A43="","",IF(H43&gt;=PARAMETER!$C$6,3,IF(H43&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="T43" s="26">
-        <f>IF($A43="","",(R43-1)*3+S43)</f>
-        <v/>
-      </c>
-      <c r="U43" s="36">
-        <f>IF($A43="","",INDEX(PARAMETER!$C$15:$C$23,T43))</f>
-        <v/>
-      </c>
-      <c r="V43" s="36">
-        <f>IF($A43="","",INDEX(PARAMETER!$C$10:$H$10,MATCH(MIN(I43:N43),I43:N43,0)))</f>
-        <v/>
-      </c>
-      <c r="W43" s="36">
-        <f>IF($A43="","",INDEX(PARAMETER!$E$15:$E$23,T43))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="27" t="n"/>
-      <c r="B44" s="27" t="n"/>
-      <c r="C44" s="27" t="n"/>
-      <c r="D44" s="27" t="n"/>
-      <c r="E44" s="31" t="n"/>
-      <c r="F44" s="32" t="n"/>
-      <c r="G44" s="33" t="n"/>
-      <c r="H44" s="33" t="n"/>
-      <c r="I44" s="33" t="n"/>
-      <c r="J44" s="33" t="n"/>
-      <c r="K44" s="33" t="n"/>
-      <c r="L44" s="33" t="n"/>
-      <c r="M44" s="33" t="n"/>
-      <c r="N44" s="33" t="n"/>
-      <c r="O44" s="34">
-        <f>IF($A44="","",ROUND((PARAMETER!$C$5-F44)/365.25,1))</f>
-        <v/>
-      </c>
-      <c r="P44" s="35">
-        <f>IF($A44="","",SUMPRODUCT(I44:N44,PARAMETER!$C$11:$H$11)/SUM(PARAMETER!$C$11:$H$11))</f>
-        <v/>
-      </c>
-      <c r="Q44" s="35">
-        <f>IF($A44="","",SUMPRODUCT((PARAMETER!$C$12:$H$12-I44:N44&gt;0)*(PARAMETER!$C$12:$H$12-I44:N44))/6)</f>
-        <v/>
-      </c>
-      <c r="R44" s="26">
-        <f>IF($A44="","",IF(G44&gt;=PARAMETER!$C$6,3,IF(G44&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="S44" s="26">
-        <f>IF($A44="","",IF(H44&gt;=PARAMETER!$C$6,3,IF(H44&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="T44" s="26">
-        <f>IF($A44="","",(R44-1)*3+S44)</f>
-        <v/>
-      </c>
-      <c r="U44" s="36">
-        <f>IF($A44="","",INDEX(PARAMETER!$C$15:$C$23,T44))</f>
-        <v/>
-      </c>
-      <c r="V44" s="36">
-        <f>IF($A44="","",INDEX(PARAMETER!$C$10:$H$10,MATCH(MIN(I44:N44),I44:N44,0)))</f>
-        <v/>
-      </c>
-      <c r="W44" s="36">
-        <f>IF($A44="","",INDEX(PARAMETER!$E$15:$E$23,T44))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="27" t="n"/>
-      <c r="B45" s="27" t="n"/>
-      <c r="C45" s="27" t="n"/>
-      <c r="D45" s="27" t="n"/>
-      <c r="E45" s="31" t="n"/>
-      <c r="F45" s="32" t="n"/>
-      <c r="G45" s="33" t="n"/>
-      <c r="H45" s="33" t="n"/>
-      <c r="I45" s="33" t="n"/>
-      <c r="J45" s="33" t="n"/>
-      <c r="K45" s="33" t="n"/>
-      <c r="L45" s="33" t="n"/>
-      <c r="M45" s="33" t="n"/>
-      <c r="N45" s="33" t="n"/>
-      <c r="O45" s="34">
-        <f>IF($A45="","",ROUND((PARAMETER!$C$5-F45)/365.25,1))</f>
-        <v/>
-      </c>
-      <c r="P45" s="35">
-        <f>IF($A45="","",SUMPRODUCT(I45:N45,PARAMETER!$C$11:$H$11)/SUM(PARAMETER!$C$11:$H$11))</f>
-        <v/>
-      </c>
-      <c r="Q45" s="35">
-        <f>IF($A45="","",SUMPRODUCT((PARAMETER!$C$12:$H$12-I45:N45&gt;0)*(PARAMETER!$C$12:$H$12-I45:N45))/6)</f>
-        <v/>
-      </c>
-      <c r="R45" s="26">
-        <f>IF($A45="","",IF(G45&gt;=PARAMETER!$C$6,3,IF(G45&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="S45" s="26">
-        <f>IF($A45="","",IF(H45&gt;=PARAMETER!$C$6,3,IF(H45&gt;=PARAMETER!$C$7,2,1)))</f>
-        <v/>
-      </c>
-      <c r="T45" s="26">
-        <f>IF($A45="","",(R45-1)*3+S45)</f>
-        <v/>
-      </c>
-      <c r="U45" s="36">
-        <f>IF($A45="","",INDEX(PARAMETER!$C$15:$C$23,T45))</f>
-        <v/>
-      </c>
-      <c r="V45" s="36">
-        <f>IF($A45="","",INDEX(PARAMETER!$C$10:$H$10,MATCH(MIN(I45:N45),I45:N45,0)))</f>
-        <v/>
-      </c>
-      <c r="W45" s="36">
-        <f>IF($A45="","",INDEX(PARAMETER!$E$15:$E$23,T45))</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
-  <autoFilter ref="A5:W45"/>
+  <autoFilter ref="A5:W25"/>
   <mergeCells count="1">
     <mergeCell ref="A3:X3"/>
   </mergeCells>
-  <conditionalFormatting sqref="U6:U45">
+  <conditionalFormatting sqref="U6:U25">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$T6=9</formula>
     </cfRule>
@@ -4747,16 +3246,16 @@
       <formula>$T6=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G6:N45">
+  <conditionalFormatting sqref="G6:N25">
     <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="2">
       <formula>PARAMETER!$C$7</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="C6:C45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C6:C25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=PARAMETER!$B$28:$B$35</formula1>
     </dataValidation>
-    <dataValidation sqref="G6:N45" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Isi angka antara 1 dan 5" type="decimal" operator="between">
+    <dataValidation sqref="G6:N25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Isi angka antara 1 dan 5" type="decimal" operator="between">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
@@ -4837,7 +3336,7 @@
         <v/>
       </c>
       <c r="C6" s="26">
-        <f>COUNTIFS(KARYAWAN!$T$6:$T$45,A6)</f>
+        <f>COUNTIFS(KARYAWAN!$T$6:$T$25,A6)</f>
         <v/>
       </c>
       <c r="D6" s="37">
@@ -4858,7 +3357,7 @@
         <v/>
       </c>
       <c r="C7" s="26">
-        <f>COUNTIFS(KARYAWAN!$T$6:$T$45,A7)</f>
+        <f>COUNTIFS(KARYAWAN!$T$6:$T$25,A7)</f>
         <v/>
       </c>
       <c r="D7" s="37">
@@ -4879,7 +3378,7 @@
         <v/>
       </c>
       <c r="C8" s="26">
-        <f>COUNTIFS(KARYAWAN!$T$6:$T$45,A8)</f>
+        <f>COUNTIFS(KARYAWAN!$T$6:$T$25,A8)</f>
         <v/>
       </c>
       <c r="D8" s="37">
@@ -4900,7 +3399,7 @@
         <v/>
       </c>
       <c r="C9" s="26">
-        <f>COUNTIFS(KARYAWAN!$T$6:$T$45,A9)</f>
+        <f>COUNTIFS(KARYAWAN!$T$6:$T$25,A9)</f>
         <v/>
       </c>
       <c r="D9" s="37">
@@ -4921,7 +3420,7 @@
         <v/>
       </c>
       <c r="C10" s="26">
-        <f>COUNTIFS(KARYAWAN!$T$6:$T$45,A10)</f>
+        <f>COUNTIFS(KARYAWAN!$T$6:$T$25,A10)</f>
         <v/>
       </c>
       <c r="D10" s="37">
@@ -4942,7 +3441,7 @@
         <v/>
       </c>
       <c r="C11" s="26">
-        <f>COUNTIFS(KARYAWAN!$T$6:$T$45,A11)</f>
+        <f>COUNTIFS(KARYAWAN!$T$6:$T$25,A11)</f>
         <v/>
       </c>
       <c r="D11" s="37">
@@ -4963,7 +3462,7 @@
         <v/>
       </c>
       <c r="C12" s="26">
-        <f>COUNTIFS(KARYAWAN!$T$6:$T$45,A12)</f>
+        <f>COUNTIFS(KARYAWAN!$T$6:$T$25,A12)</f>
         <v/>
       </c>
       <c r="D12" s="37">
@@ -4984,7 +3483,7 @@
         <v/>
       </c>
       <c r="C13" s="26">
-        <f>COUNTIFS(KARYAWAN!$T$6:$T$45,A13)</f>
+        <f>COUNTIFS(KARYAWAN!$T$6:$T$25,A13)</f>
         <v/>
       </c>
       <c r="D13" s="37">
@@ -5005,7 +3504,7 @@
         <v/>
       </c>
       <c r="C14" s="26">
-        <f>COUNTIFS(KARYAWAN!$T$6:$T$45,A14)</f>
+        <f>COUNTIFS(KARYAWAN!$T$6:$T$25,A14)</f>
         <v/>
       </c>
       <c r="D14" s="37">
@@ -5067,7 +3566,7 @@
       <c r="B19" s="24" t="n"/>
       <c r="C19" s="25" t="n"/>
       <c r="D19" s="43">
-        <f>IFERROR(AVERAGE(KARYAWAN!$G$6:$G$45),0)</f>
+        <f>IFERROR(AVERAGE(KARYAWAN!$G$6:$G$25),0)</f>
         <v/>
       </c>
     </row>
@@ -5080,7 +3579,7 @@
       <c r="B20" s="24" t="n"/>
       <c r="C20" s="25" t="n"/>
       <c r="D20" s="43">
-        <f>IFERROR(AVERAGE(KARYAWAN!$H$6:$H$45),0)</f>
+        <f>IFERROR(AVERAGE(KARYAWAN!$H$6:$H$25),0)</f>
         <v/>
       </c>
     </row>
@@ -5093,7 +3592,7 @@
       <c r="B21" s="24" t="n"/>
       <c r="C21" s="25" t="n"/>
       <c r="D21" s="43">
-        <f>IFERROR(AVERAGE(KARYAWAN!$P$6:$P$45),0)</f>
+        <f>IFERROR(AVERAGE(KARYAWAN!$P$6:$P$25),0)</f>
         <v/>
       </c>
     </row>
@@ -5106,7 +3605,7 @@
       <c r="B22" s="24" t="n"/>
       <c r="C22" s="25" t="n"/>
       <c r="D22" s="44">
-        <f>IF(C15=0,0,COUNTIFS(KARYAWAN!$S$6:$S$45,3)/C15)</f>
+        <f>IF(C15=0,0,COUNTIFS(KARYAWAN!$S$6:$S$25,3)/C15)</f>
         <v/>
       </c>
     </row>
@@ -5151,4 +3650,268 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C0392B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="45" t="inlineStr">
+        <is>
+          <t>Fitur Versi Lengkap</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="B3" s="46" t="inlineStr">
+        <is>
+          <t>MATRIKS 9BOX</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="B5" s="47" t="inlineStr">
+        <is>
+          <t>Matriks 3×3 kinerja × potensi dengan jumlah dan persentase karyawan per kotak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>• Sheet ini hanya tersedia di versi lengkap, lengkap dengan rumus dan grafik yang bekerja dari data Anda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>• Kapasitas data versi lengkap jauh lebih besar dibanding demo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="48" t="inlineStr">
+        <is>
+          <t>• Pesan versi lengkap lewat WhatsApp 089623291732.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="B5:C5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C0392B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="45" t="inlineStr">
+        <is>
+          <t>Fitur Versi Lengkap</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="B3" s="46" t="inlineStr">
+        <is>
+          <t>KOMPETENSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="B5" s="47" t="inlineStr">
+        <is>
+          <t>Rata-rata kompetensi per departemen, gap terhadap target, dan peta panas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>• Sheet ini hanya tersedia di versi lengkap, lengkap dengan rumus dan grafik yang bekerja dari data Anda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>• Kapasitas data versi lengkap jauh lebih besar dibanding demo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="48" t="inlineStr">
+        <is>
+          <t>• Pesan versi lengkap lewat WhatsApp 089623291732.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="B5:C5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C0392B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="45" t="inlineStr">
+        <is>
+          <t>Fitur Versi Lengkap</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="B3" s="46" t="inlineStr">
+        <is>
+          <t>SUKSESI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="B5" s="47" t="inlineStr">
+        <is>
+          <t>10 talenta teratas (potensi dan kinerja tertinggi) untuk daftar suksesi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>• Sheet ini hanya tersedia di versi lengkap, lengkap dengan rumus dan grafik yang bekerja dari data Anda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>• Kapasitas data versi lengkap jauh lebih besar dibanding demo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="48" t="inlineStr">
+        <is>
+          <t>• Pesan versi lengkap lewat WhatsApp 089623291732.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="B5:C5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C0392B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="45" t="inlineStr">
+        <is>
+          <t>Fitur Versi Lengkap</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="B3" s="46" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="B5" s="47" t="inlineStr">
+        <is>
+          <t>Grafik sebaran kotak dan kompetensi terhadap target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>• Sheet ini hanya tersedia di versi lengkap, lengkap dengan rumus dan grafik yang bekerja dari data Anda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>• Kapasitas data versi lengkap jauh lebih besar dibanding demo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="48" t="inlineStr">
+        <is>
+          <t>• Pesan versi lengkap lewat WhatsApp 089623291732.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="B5:C5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>